--- a/data/trans_orig/P39A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39A-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2012 (tasa de respuesta: 96,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>25683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>49739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14050</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>43647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74798</t>
+          <t>74244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>66238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100885</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53944</t>
+          <t>53367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86838</t>
+          <t>82578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129512</t>
+          <t>127438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69724</t>
+          <t>70426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103676</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56702</t>
+          <t>56145</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87950</t>
+          <t>87105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>135577</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>181681</t>
+          <t>183484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>41662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>42700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>68519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103611</t>
+          <t>104146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95241</t>
+          <t>96280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134796</t>
+          <t>133515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74780</t>
+          <t>74325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109472</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180240</t>
+          <t>182629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229699</t>
+          <t>231825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70278</t>
+          <t>69892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>78756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51555</t>
+          <t>52755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>82602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>107982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153159</t>
+          <t>152289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93602</t>
+          <t>95090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132625</t>
+          <t>132783</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101876</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172694</t>
+          <t>174985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224668</t>
+          <t>223031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40165</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71320</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48640</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71961</t>
+          <t>72419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94850</t>
+          <t>95671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135804</t>
+          <t>133374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70225</t>
+          <t>69348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103014</t>
+          <t>102900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176779</t>
+          <t>176108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226264</t>
+          <t>227015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>51331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25175</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>39573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>89353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130776</t>
+          <t>128916</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60382</t>
+          <t>59549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131881</t>
+          <t>132115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178464</t>
+          <t>176625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106037</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147357</t>
+          <t>147351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55743</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146053</t>
+          <t>145043</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196368</t>
+          <t>193624</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53159</t>
+          <t>54529</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>87171</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>83872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121964</t>
+          <t>124735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175189</t>
+          <t>176748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223092</t>
+          <t>223425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>77702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>107440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268951</t>
+          <t>266065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>325501</t>
+          <t>324254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67646</t>
+          <t>67734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105557</t>
+          <t>103113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87951</t>
+          <t>85797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127828</t>
+          <t>129184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178677</t>
+          <t>178822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168581</t>
+          <t>169654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>219977</t>
+          <t>219964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>98788</t>
+          <t>98266</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>140115</t>
+          <t>139293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280569</t>
+          <t>282590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>347772</t>
+          <t>347087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>212589</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266770</t>
+          <t>265709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130421</t>
+          <t>130739</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174677</t>
+          <t>176495</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>356786</t>
+          <t>353584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>429534</t>
+          <t>422571</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>82042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122054</t>
+          <t>121097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>61539</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95951</t>
+          <t>96898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,47 +3167,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>178638</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>151408</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>207164</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>9,28%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>178638</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>153374</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>203208</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>321364</t>
+          <t>324878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>381830</t>
+          <t>385019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>220999</t>
+          <t>219498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>273648</t>
+          <t>270779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>555785</t>
+          <t>558820</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>636977</t>
+          <t>634800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31144</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>58003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69331</t>
+          <t>68350</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76578</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115106</t>
+          <t>117663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116645</t>
+          <t>116284</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87454</t>
+          <t>86552</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124375</t>
+          <t>126041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>177726</t>
+          <t>179592</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>230944</t>
+          <t>231271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78090</t>
+          <t>79033</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>112044</t>
+          <t>112796</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>105952</t>
+          <t>104569</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>145206</t>
+          <t>145549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>193302</t>
+          <t>195108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>246739</t>
+          <t>252966</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35860</t>
+          <t>36848</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>63810</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77150</t>
+          <t>77230</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>113447</t>
+          <t>113183</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>120833</t>
+          <t>120639</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>165983</t>
+          <t>166478</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>102900</t>
+          <t>104582</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>140026</t>
+          <t>141411</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>274168</t>
+          <t>273265</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>326783</t>
+          <t>325296</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>389671</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>452467</t>
+          <t>454580</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,97%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78199</t>
+          <t>77483</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>67223</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>102516</t>
+          <t>100886</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33733</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>53942</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>80510</t>
+          <t>81602</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>118392</t>
+          <t>120478</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>121315</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>166816</t>
+          <t>167886</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>159447</t>
+          <t>156870</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>210178</t>
+          <t>206919</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>179944</t>
+          <t>178082</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>231644</t>
+          <t>229333</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>126831</t>
+          <t>125648</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>172456</t>
+          <t>171695</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>136479</t>
+          <t>138466</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>183999</t>
+          <t>186483</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>403881</t>
+          <t>408076</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>467456</t>
+          <t>467157</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>422689</t>
+          <t>419702</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>487782</t>
+          <t>486585</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>216643</t>
+          <t>218854</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>280369</t>
+          <t>278806</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>218326</t>
+          <t>217070</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>279715</t>
+          <t>280058</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>453448</t>
+          <t>457560</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>544946</t>
+          <t>540198</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>545189</t>
+          <t>543761</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>633208</t>
+          <t>632034</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>462623</t>
+          <t>458370</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>545042</t>
+          <t>545672</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1032930</t>
+          <t>1025221</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1157752</t>
+          <t>1153128</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>637623</t>
+          <t>637706</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>728314</t>
+          <t>730323</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>611020</t>
+          <t>607501</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>706316</t>
+          <t>706807</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1274935</t>
+          <t>1263814</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1405012</t>
+          <t>1400951</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>304482</t>
+          <t>305681</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>375333</t>
+          <t>375628</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>381332</t>
+          <t>380350</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>458465</t>
+          <t>464301</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>705238</t>
+          <t>708324</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>809825</t>
+          <t>810375</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>876149</t>
+          <t>872544</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>973883</t>
+          <t>975299</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1191647</t>
+          <t>1195858</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1300245</t>
+          <t>1316101</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2098431</t>
+          <t>2098066</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2253872</t>
+          <t>2246637</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2016 (tasa de respuesta: 96,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>61543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61888</t>
+          <t>61125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96165</t>
+          <t>94865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65972</t>
+          <t>66784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98270</t>
+          <t>98798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78470</t>
+          <t>78535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110132</t>
+          <t>109890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154671</t>
+          <t>153964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200053</t>
+          <t>200303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96854</t>
+          <t>96760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131728</t>
+          <t>131818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66777</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97598</t>
+          <t>97795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170896</t>
+          <t>171436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219969</t>
+          <t>218195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>58459</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64647</t>
+          <t>64411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>75757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114492</t>
+          <t>113312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60242</t>
+          <t>60054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92004</t>
+          <t>93873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47081</t>
+          <t>46884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>75022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114344</t>
+          <t>114903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157044</t>
+          <t>158031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46101</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52197</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85029</t>
+          <t>84803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62327</t>
+          <t>61012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>92645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102058</t>
+          <t>101343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140314</t>
+          <t>141294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>183511</t>
+          <t>187255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>74695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106741</t>
+          <t>106081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69313</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102725</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>152559</t>
+          <t>150877</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>198150</t>
+          <t>197241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60754</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54693</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72468</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108515</t>
+          <t>106683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>59951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>91613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56921</t>
+          <t>56725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88405</t>
+          <t>86278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123916</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167990</t>
+          <t>169019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61012</t>
+          <t>59565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>91456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128972</t>
+          <t>128289</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41047</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>120101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161176</t>
+          <t>163650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100911</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138567</t>
+          <t>139429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>48501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135765</t>
+          <t>135305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177966</t>
+          <t>177381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88484</t>
+          <t>89910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73931</t>
+          <t>72612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109899</t>
+          <t>108414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81790</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117236</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61781</t>
+          <t>62603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124670</t>
+          <t>123432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169131</t>
+          <t>168511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>88825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127459</t>
+          <t>128395</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94952</t>
+          <t>94840</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160071</t>
+          <t>158105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>211717</t>
+          <t>210042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>234947</t>
+          <t>232955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291861</t>
+          <t>287727</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>159825</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>206462</t>
+          <t>208321</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>407716</t>
+          <t>407331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479381</t>
+          <t>477905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>228262</t>
+          <t>227275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>284599</t>
+          <t>280210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160022</t>
+          <t>161400</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>206382</t>
+          <t>209973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>402902</t>
+          <t>405722</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>474724</t>
+          <t>477545</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>115070</t>
+          <t>113444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158175</t>
+          <t>157328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71307</t>
+          <t>72018</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105918</t>
+          <t>107673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197153</t>
+          <t>194749</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253988</t>
+          <t>249515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177718</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>226586</t>
+          <t>227875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>163631</t>
+          <t>160949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>206957</t>
+          <t>210074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>348219</t>
+          <t>349068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>416777</t>
+          <t>419736</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57746</t>
+          <t>57695</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90565</t>
+          <t>89236</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>86186</t>
+          <t>84186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>119715</t>
+          <t>117689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>163375</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105689</t>
+          <t>105617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>143847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>117055</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>160326</t>
+          <t>160296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232506</t>
+          <t>233286</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>289811</t>
+          <t>292837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>123433</t>
+          <t>122404</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>164776</t>
+          <t>163759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152651</t>
+          <t>150930</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>198717</t>
+          <t>195821</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>287263</t>
+          <t>283866</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>346640</t>
+          <t>347276</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>70379</t>
+          <t>68757</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>127369</t>
+          <t>127145</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>137319</t>
+          <t>137407</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>185922</t>
+          <t>185093</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>83079</t>
+          <t>81696</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>120936</t>
+          <t>117207</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>138818</t>
+          <t>139870</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>183228</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230946</t>
+          <t>232881</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>287904</t>
+          <t>293501</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>44504</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>75103</t>
+          <t>77074</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>68738</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>106188</t>
+          <t>104593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>64194</t>
+          <t>63844</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>194050</t>
+          <t>193886</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>245175</t>
+          <t>248247</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>241489</t>
+          <t>239245</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>298645</t>
+          <t>298499</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>227521</t>
+          <t>224220</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>285079</t>
+          <t>281724</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>258979</t>
+          <t>256996</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>318160</t>
+          <t>317886</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>130091</t>
+          <t>131213</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>176590</t>
+          <t>177394</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>142021</t>
+          <t>140283</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>192470</t>
+          <t>190168</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>215189</t>
+          <t>215418</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>271497</t>
+          <t>270992</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>230692</t>
+          <t>229810</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>289451</t>
+          <t>290144</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>296630</t>
+          <t>293795</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>365464</t>
+          <t>361776</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>253216</t>
+          <t>250284</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>319134</t>
+          <t>317171</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>565430</t>
+          <t>568284</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>659068</t>
+          <t>659607</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>657146</t>
+          <t>653528</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>751396</t>
+          <t>751952</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>702851</t>
+          <t>697559</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>795387</t>
+          <t>797850</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1392249</t>
+          <t>1389311</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1526967</t>
+          <t>1514532</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>702969</t>
+          <t>706154</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>800112</t>
+          <t>800157</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>767014</t>
+          <t>767583</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>864619</t>
+          <t>863746</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1499200</t>
+          <t>1495240</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1639185</t>
+          <t>1634564</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>329715</t>
+          <t>329315</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>402091</t>
+          <t>401927</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>418960</t>
+          <t>419720</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>498615</t>
+          <t>503146</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>765658</t>
+          <t>765112</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>876956</t>
+          <t>870712</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>519698</t>
+          <t>517732</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>607865</t>
+          <t>605293</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>721722</t>
+          <t>719500</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>817426</t>
+          <t>814826</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1271430</t>
+          <t>1267967</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1406400</t>
+          <t>1394645</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la tensión arterial en 2023 (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>37131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61989</t>
+          <t>60796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>98357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137505</t>
+          <t>136882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78769</t>
+          <t>77006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107600</t>
+          <t>107027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185772</t>
+          <t>185897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234739</t>
+          <t>232435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122836</t>
+          <t>121006</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164212</t>
+          <t>162438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91066</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121349</t>
+          <t>122222</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224184</t>
+          <t>224462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>275106</t>
+          <t>273890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54200</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81745</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56466</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>81559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117781</t>
+          <t>116970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153962</t>
+          <t>156067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109403</t>
+          <t>112780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98599</t>
+          <t>98301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>129821</t>
+          <t>129160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184414</t>
+          <t>185925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229789</t>
+          <t>232156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39802</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>37075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40320</t>
+          <t>40899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67245</t>
+          <t>67317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76338</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110069</t>
+          <t>110586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93461</t>
+          <t>95463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148404</t>
+          <t>150941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>193791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87920</t>
+          <t>87523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125792</t>
+          <t>125112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110774</t>
+          <t>110771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175963</t>
+          <t>179158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226712</t>
+          <t>225624</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63274</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95748</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50136</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161614</t>
+          <t>161245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116938</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86388</t>
+          <t>86833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151668</t>
+          <t>152803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195636</t>
+          <t>192466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54351</t>
+          <t>54760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87431</t>
+          <t>85467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122915</t>
+          <t>121223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37368</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114347</t>
+          <t>115383</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153683</t>
+          <t>152318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82939</t>
+          <t>82010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115851</t>
+          <t>114550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27697</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>114222</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152268</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58354</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87135</t>
+          <t>85502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83225</t>
+          <t>83691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115347</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61047</t>
+          <t>60515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90865</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39143</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58857</t>
+          <t>57928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104744</t>
+          <t>105456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141942</t>
+          <t>142200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53799</t>
+          <t>51931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88207</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105394</t>
+          <t>106779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>102332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176926</t>
+          <t>176788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186635</t>
+          <t>190346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243470</t>
+          <t>248287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>209191</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>657781</t>
+          <t>661453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>422203</t>
+          <t>420933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>975906</t>
+          <t>976519</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226986</t>
+          <t>222832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283139</t>
+          <t>282115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>102333</t>
+          <t>88356</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>273540</t>
+          <t>271592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>308039</t>
+          <t>307695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>527017</t>
+          <t>529765</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>131266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178487</t>
+          <t>178039</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>42521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123890</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162361</t>
+          <t>161551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>289415</t>
+          <t>287874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>164794</t>
+          <t>166509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>214509</t>
+          <t>213842</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75269</t>
+          <t>75757</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>216416</t>
+          <t>215885</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>237291</t>
+          <t>239932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>409258</t>
+          <t>407926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>57707</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35668</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>73981</t>
+          <t>74587</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113394</t>
+          <t>112096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87299</t>
+          <t>84626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127391</t>
+          <t>125451</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>100888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>142195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>200467</t>
+          <t>200070</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>258096</t>
+          <t>259810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>96628</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134555</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>189164</t>
+          <t>186306</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>301272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>296915</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>416336</t>
+          <t>408242</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>52333</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>81593</t>
+          <t>83588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>102246</t>
+          <t>101564</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>139769</t>
+          <t>138910</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>161234</t>
+          <t>163396</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>208964</t>
+          <t>211516</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55958</t>
+          <t>56567</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85156</t>
+          <t>84229</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>160045</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>211325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>225428</t>
+          <t>225376</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>283924</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63573</t>
+          <t>62566</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>56046</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>93609</t>
+          <t>94698</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36314</t>
+          <t>33567</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>131226</t>
+          <t>132402</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>172673</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>148864</t>
+          <t>148503</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>199717</t>
+          <t>196431</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>49678</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>142870</t>
+          <t>143680</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>182068</t>
+          <t>181470</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>171439</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>221117</t>
+          <t>222573</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>105851</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>137809</t>
+          <t>138613</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>113626</t>
+          <t>114489</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>152063</t>
+          <t>153609</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>132277</t>
+          <t>135090</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170809</t>
+          <t>170694</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>142069</t>
+          <t>141780</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>183515</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>184607</t>
+          <t>184421</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>249358</t>
+          <t>249193</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>183117</t>
+          <t>189912</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>269802</t>
+          <t>266919</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>395803</t>
+          <t>389356</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>499293</t>
+          <t>495585</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>608926</t>
+          <t>609402</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>703562</t>
+          <t>708529</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>673069</t>
+          <t>675672</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1378069</t>
+          <t>1302590</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1321508</t>
+          <t>1329010</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2136994</t>
+          <t>2086802</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>699461</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>796062</t>
+          <t>795877</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>654810</t>
+          <t>659907</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>912951</t>
+          <t>907446</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1375836</t>
+          <t>1383598</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1664543</t>
+          <t>1667428</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>406160</t>
+          <t>409530</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>484458</t>
+          <t>487409</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>369720</t>
+          <t>401606</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>535837</t>
+          <t>542340</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>820659</t>
+          <t>827323</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1002106</t>
+          <t>998670</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>496585</t>
+          <t>498263</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>575433</t>
+          <t>579853</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>578090</t>
+          <t>603558</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>803154</t>
+          <t>804777</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1117733</t>
+          <t>1127769</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1350678</t>
+          <t>1348432</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
